--- a/CodeCC/申万一级行业年度收益率矩阵.xlsx
+++ b/CodeCC/申万一级行业年度收益率矩阵.xlsx
@@ -570,7 +570,7 @@
         <v>14.14136065588236</v>
       </c>
       <c r="L2">
-        <v>2.946947119432619</v>
+        <v>1.005290798084202</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -608,7 +608,7 @@
         <v>-2.926858521648956</v>
       </c>
       <c r="L3">
-        <v>17.51304812988854</v>
+        <v>12.08705018289069</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -646,7 +646,7 @@
         <v>96.45595704813393</v>
       </c>
       <c r="L4">
-        <v>-7.312120808247036</v>
+        <v>-3.051497644447787</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -684,7 +684,7 @@
         <v>36.1055252918288</v>
       </c>
       <c r="L5">
-        <v>-6.139423750095974</v>
+        <v>-3.15067503173031</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -722,7 +722,7 @@
         <v>29.08185792402751</v>
       </c>
       <c r="L6">
-        <v>-17.68242052623076</v>
+        <v>-16.03639956867564</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -760,7 +760,7 @@
         <v>19.92099663310498</v>
       </c>
       <c r="L7">
-        <v>-20.1813442824221</v>
+        <v>-19.03108615362942</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -798,7 +798,7 @@
         <v>45.96042606509039</v>
       </c>
       <c r="L8">
-        <v>-10.50209245647594</v>
+        <v>-7.155133072464048</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -836,7 +836,7 @@
         <v>40.60538944259875</v>
       </c>
       <c r="L9">
-        <v>-22.14835773157829</v>
+        <v>-18.9784721367942</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -874,7 +874,7 @@
         <v>45.25972403266223</v>
       </c>
       <c r="L10">
-        <v>-3.065525551391413</v>
+        <v>0.4503678997186844</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -912,7 +912,7 @@
         <v>10.34959079390136</v>
       </c>
       <c r="L11">
-        <v>-11.70582445927729</v>
+        <v>-9.174444584376984</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -950,7 +950,7 @@
         <v>23.88367591142406</v>
       </c>
       <c r="L12">
-        <v>4.035936065612811</v>
+        <v>6.971178952884749</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -988,7 +988,7 @@
         <v>4.009268297132862</v>
       </c>
       <c r="L13">
-        <v>-9.989926937305082</v>
+        <v>-7.801125191894043</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1026,7 +1026,7 @@
         <v>20.88482218658616</v>
       </c>
       <c r="L14">
-        <v>-21.17219519747081</v>
+        <v>-16.1089246864993</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1064,7 +1064,7 @@
         <v>3.713513073366004</v>
       </c>
       <c r="L15">
-        <v>4.919801894882814</v>
+        <v>2.788981941577862</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1102,7 +1102,7 @@
         <v>19.46152344703069</v>
       </c>
       <c r="L16">
-        <v>-8.452948954505002</v>
+        <v>-3.384598368032332</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1140,7 +1140,7 @@
         <v>28.13823746271222</v>
       </c>
       <c r="L17">
-        <v>-21.52940560382233</v>
+        <v>-17.90270615343183</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1178,7 +1178,7 @@
         <v>6.084119720622683</v>
       </c>
       <c r="L18">
-        <v>-29.07394083740624</v>
+        <v>-24.67768212303901</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1216,7 +1216,7 @@
         <v>9.380393981770574</v>
       </c>
       <c r="L19">
-        <v>-9.006873666745662</v>
+        <v>-6.78968982163215</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1254,7 +1254,7 @@
         <v>-7.978261325961522</v>
       </c>
       <c r="L20">
-        <v>-16.07340519904177</v>
+        <v>-14.56352482156865</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1292,7 +1292,7 @@
         <v>13.07854746662034</v>
       </c>
       <c r="L21">
-        <v>-17.01967429163136</v>
+        <v>-10.98089052056859</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1330,7 +1330,7 @@
         <v>14.47543367538382</v>
       </c>
       <c r="L22">
-        <v>-8.763724025888964</v>
+        <v>-7.403768047585368</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1368,7 +1368,7 @@
         <v>10.03237789866307</v>
       </c>
       <c r="L23">
-        <v>-24.54062818263317</v>
+        <v>-17.73941869734189</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1406,7 +1406,7 @@
         <v>1.250245860860111</v>
       </c>
       <c r="L24">
-        <v>-22.85417121605406</v>
+        <v>-20.34200887440089</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1444,7 +1444,7 @@
         <v>53.36425176841124</v>
       </c>
       <c r="L25">
-        <v>29.54866506568725</v>
+        <v>25.55136671846305</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1482,7 +1482,7 @@
         <v>23.25358082155496</v>
       </c>
       <c r="L26">
-        <v>-18.7426083869702</v>
+        <v>-12.36634375554664</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1520,7 +1520,7 @@
         <v>90.41474718177508</v>
       </c>
       <c r="L27">
-        <v>34.31073261899722</v>
+        <v>26.16432361075738</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1558,7 +1558,7 @@
         <v>29.93421574066735</v>
       </c>
       <c r="L28">
-        <v>-26.06973801377887</v>
+        <v>-15.96522472700005</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1596,7 +1596,7 @@
         <v>9.402093887553576</v>
       </c>
       <c r="L29">
-        <v>-4.734353748839625</v>
+        <v>-5.134220380005239</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1634,7 +1634,7 @@
         <v>15.74575984673465</v>
       </c>
       <c r="L30">
-        <v>-14.50425276831144</v>
+        <v>-15.69748232339919</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1672,7 +1672,7 @@
         <v>3.590389167067443</v>
       </c>
       <c r="L31">
-        <v>-19.52811583264823</v>
+        <v>-16.19024515155191</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1710,7 +1710,7 @@
         <v>43.2586095459973</v>
       </c>
       <c r="L32">
-        <v>-2.249997507204171</v>
+        <v>4.189392655226398</v>
       </c>
     </row>
   </sheetData>
